--- a/inst/model/외부데이터DB_테이블정의서_20260114.xlsx
+++ b/inst/model/외부데이터DB_테이블정의서_20260114.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10110"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E665FF54-B84C-EE49-8A9A-DC580CDE1A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99180DED-C68F-B141-AAE8-53B494C84A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" tabRatio="849" firstSheet="10" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27040" yWindow="600" windowWidth="38400" windowHeight="19980" tabRatio="849" firstSheet="27" activeTab="38" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="테이블_목록" sheetId="8" r:id="rId1"/>
@@ -3810,18 +3810,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3854,6 +3842,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5456,11 +5456,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -5479,9 +5479,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -5502,7 +5502,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -5527,7 +5527,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -5537,12 +5537,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>243</v>
       </c>
@@ -5560,22 +5560,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>237</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -5583,14 +5583,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -5813,6 +5813,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -5825,13 +5832,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -5868,11 +5868,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -5891,9 +5891,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -5914,7 +5914,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -5939,7 +5939,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -5949,12 +5949,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>268</v>
       </c>
@@ -5972,22 +5972,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>249</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -5995,14 +5995,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -6625,6 +6625,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -6637,13 +6644,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -6677,11 +6677,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -6700,9 +6700,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -6723,7 +6723,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -6748,7 +6748,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46037</v>
       </c>
       <c r="N4" s="99"/>
@@ -6758,12 +6758,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>288</v>
       </c>
@@ -6781,22 +6781,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>166</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -6804,14 +6804,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -7192,6 +7192,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -7204,13 +7211,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -7244,11 +7244,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -7267,9 +7267,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -7290,7 +7290,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -7315,7 +7315,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -7325,12 +7325,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>280</v>
       </c>
@@ -7348,22 +7348,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -7624,6 +7624,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -7636,13 +7643,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -7676,11 +7676,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -7699,9 +7699,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -7722,7 +7722,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -7747,7 +7747,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -7757,12 +7757,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>270</v>
       </c>
@@ -7780,22 +7780,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>301</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -7803,14 +7803,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -8193,6 +8193,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -8205,13 +8212,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -8245,11 +8245,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -8268,9 +8268,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -8291,7 +8291,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -8316,7 +8316,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45973</v>
       </c>
       <c r="N4" s="99"/>
@@ -8326,12 +8326,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>271</v>
       </c>
@@ -8349,22 +8349,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>273</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -8372,14 +8372,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -8870,6 +8870,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -8882,13 +8889,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -8922,11 +8922,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -8945,9 +8945,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -8968,7 +8968,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -8993,7 +8993,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46038</v>
       </c>
       <c r="N4" s="99"/>
@@ -9003,12 +9003,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>102</v>
       </c>
@@ -9026,22 +9026,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>715</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -9049,14 +9049,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -9273,6 +9273,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -9285,13 +9292,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -9325,11 +9325,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -9348,9 +9348,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -9371,7 +9371,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -9396,7 +9396,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46038</v>
       </c>
       <c r="N4" s="99"/>
@@ -9406,12 +9406,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>103</v>
       </c>
@@ -9429,22 +9429,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>722</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -9452,14 +9452,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -9732,6 +9732,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -9744,13 +9751,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -9784,11 +9784,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -9807,9 +9807,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -9830,7 +9830,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -9855,7 +9855,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46038</v>
       </c>
       <c r="N4" s="99"/>
@@ -9865,12 +9865,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>104</v>
       </c>
@@ -9888,22 +9888,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>727</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -9911,14 +9911,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -10247,6 +10247,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -10259,13 +10266,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -10299,11 +10299,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -10322,9 +10322,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -10345,7 +10345,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -10370,7 +10370,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45985</v>
       </c>
       <c r="N4" s="99"/>
@@ -10380,12 +10380,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>536</v>
       </c>
@@ -10403,22 +10403,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>538</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -10426,14 +10426,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -10625,13 +10625,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -10644,6 +10637,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -10677,11 +10677,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -10700,9 +10700,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -10723,7 +10723,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -10748,7 +10748,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -10758,12 +10758,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>63</v>
       </c>
@@ -10781,22 +10781,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -10804,14 +10804,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -11084,6 +11084,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -11096,13 +11103,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -11136,11 +11136,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -11159,9 +11159,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -11182,7 +11182,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -11207,7 +11207,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45980</v>
       </c>
       <c r="N4" s="99"/>
@@ -11217,12 +11217,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>433</v>
       </c>
@@ -11240,22 +11240,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>435</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -11263,14 +11263,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -11609,13 +11609,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -11628,6 +11621,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -11661,11 +11661,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -11684,9 +11684,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -11707,7 +11707,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -11732,7 +11732,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -11742,12 +11742,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>353</v>
       </c>
@@ -11765,22 +11765,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>437</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -11788,14 +11788,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -12209,6 +12209,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -12221,13 +12228,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -12261,11 +12261,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -12284,9 +12284,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -12307,7 +12307,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -12332,7 +12332,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -12342,12 +12342,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>352</v>
       </c>
@@ -12365,22 +12365,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>333</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -12388,14 +12388,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -12780,6 +12780,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -12792,13 +12799,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -12832,11 +12832,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -12855,9 +12855,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -12878,7 +12878,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -12903,7 +12903,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -12913,12 +12913,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>354</v>
       </c>
@@ -12936,22 +12936,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>334</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -12959,14 +12959,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -13376,6 +13376,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -13388,13 +13395,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -13431,11 +13431,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -13454,9 +13454,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -13477,7 +13477,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -13502,7 +13502,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45975</v>
       </c>
       <c r="N4" s="99"/>
@@ -13512,12 +13512,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>424</v>
       </c>
@@ -13535,22 +13535,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>370</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -13558,14 +13558,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -13896,6 +13896,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -13908,13 +13915,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -13948,11 +13948,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -13971,9 +13971,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -13994,7 +13994,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -14019,7 +14019,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45976</v>
       </c>
       <c r="N4" s="99"/>
@@ -14029,12 +14029,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>387</v>
       </c>
@@ -14052,22 +14052,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>390</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -14075,14 +14075,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -14440,6 +14440,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -14452,13 +14459,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -14492,11 +14492,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -14515,9 +14515,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -14538,7 +14538,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -14563,7 +14563,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45976</v>
       </c>
       <c r="N4" s="99"/>
@@ -14573,12 +14573,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>356</v>
       </c>
@@ -14596,22 +14596,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>383</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -14619,14 +14619,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -14872,6 +14872,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -14884,13 +14891,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -14924,11 +14924,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -14947,9 +14947,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -14970,7 +14970,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -14995,7 +14995,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45979</v>
       </c>
       <c r="N4" s="99"/>
@@ -15005,12 +15005,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>429</v>
       </c>
@@ -15028,22 +15028,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>428</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -15051,14 +15051,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -15541,6 +15541,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -15553,13 +15560,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -15593,11 +15593,11 @@
   <sheetData>
     <row r="1" spans="2:18" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:18" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -15616,9 +15616,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:18" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -15639,7 +15639,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -15664,7 +15664,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45987</v>
       </c>
       <c r="N4" s="99"/>
@@ -15674,12 +15674,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>405</v>
       </c>
@@ -15697,22 +15697,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:18" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>404</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:18" ht="9.75" customHeight="1" thickBot="1"/>
@@ -15720,14 +15720,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -16162,13 +16162,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -16181,6 +16174,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -16214,11 +16214,11 @@
   <sheetData>
     <row r="1" spans="2:17" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:17" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -16237,9 +16237,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:17" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -16260,7 +16260,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -16285,7 +16285,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46001</v>
       </c>
       <c r="N4" s="99"/>
@@ -16295,12 +16295,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:17">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>665</v>
       </c>
@@ -16318,22 +16318,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:17" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>680</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:17" ht="9.75" customHeight="1" thickBot="1"/>
@@ -16341,14 +16341,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -16601,6 +16601,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -16613,13 +16620,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -16656,11 +16656,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -16679,9 +16679,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -16702,7 +16702,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -16727,7 +16727,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -16737,12 +16737,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>50</v>
       </c>
@@ -16760,22 +16760,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -16783,14 +16783,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -17566,13 +17566,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -17585,6 +17578,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -17618,11 +17618,11 @@
   <sheetData>
     <row r="1" spans="2:17" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:17" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -17641,9 +17641,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:17" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -17664,7 +17664,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -17689,7 +17689,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46001</v>
       </c>
       <c r="N4" s="99"/>
@@ -17699,12 +17699,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:17">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>664</v>
       </c>
@@ -17722,22 +17722,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:17" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>686</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:17" ht="9.75" customHeight="1" thickBot="1"/>
@@ -17745,14 +17745,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -18185,6 +18185,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -18197,13 +18204,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -18237,11 +18237,11 @@
   <sheetData>
     <row r="1" spans="2:17" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:17" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -18260,9 +18260,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:17" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -18283,7 +18283,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -18308,7 +18308,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46001</v>
       </c>
       <c r="N4" s="99"/>
@@ -18318,12 +18318,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:17">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>694</v>
       </c>
@@ -18341,22 +18341,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:17" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>696</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:17" ht="9.75" customHeight="1" thickBot="1"/>
@@ -18364,14 +18364,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -18698,6 +18698,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -18710,13 +18717,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -18750,11 +18750,11 @@
   <sheetData>
     <row r="1" spans="2:17" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:17" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -18773,9 +18773,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:17" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -18796,7 +18796,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -18821,7 +18821,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45986</v>
       </c>
       <c r="N4" s="99"/>
@@ -18831,12 +18831,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:17">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>509</v>
       </c>
@@ -18854,22 +18854,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:17" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>591</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:17" ht="9.75" customHeight="1" thickBot="1"/>
@@ -18877,14 +18877,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -19335,6 +19335,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -19347,13 +19354,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -19387,11 +19387,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -19410,9 +19410,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -19433,7 +19433,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -19458,7 +19458,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46000</v>
       </c>
       <c r="N4" s="99"/>
@@ -19468,12 +19468,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>635</v>
       </c>
@@ -19491,22 +19491,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>606</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -19514,14 +19514,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -20359,6 +20359,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -20371,13 +20378,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -20411,11 +20411,11 @@
   <sheetData>
     <row r="1" spans="2:17" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:17" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -20434,9 +20434,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:17" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -20457,7 +20457,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:17">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -20482,7 +20482,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45986</v>
       </c>
       <c r="N4" s="99"/>
@@ -20492,12 +20492,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:17">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>592</v>
       </c>
@@ -20515,22 +20515,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:17" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>594</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:17" ht="9.75" customHeight="1" thickBot="1"/>
@@ -20538,14 +20538,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -20924,13 +20924,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -20943,6 +20936,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -20976,11 +20976,11 @@
   <sheetData>
     <row r="1" spans="2:18" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:18" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -20999,9 +20999,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:18" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -21022,7 +21022,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -21047,7 +21047,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45985</v>
       </c>
       <c r="N4" s="99"/>
@@ -21057,12 +21057,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>465</v>
       </c>
@@ -21080,22 +21080,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:18" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>467</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:18" ht="9.75" customHeight="1" thickBot="1"/>
@@ -21103,14 +21103,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -21381,13 +21381,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -21400,6 +21393,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -21433,11 +21433,11 @@
   <sheetData>
     <row r="1" spans="2:18" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:18" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -21456,9 +21456,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:18" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -21479,7 +21479,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -21504,7 +21504,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45997</v>
       </c>
       <c r="N4" s="99"/>
@@ -21514,12 +21514,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>550</v>
       </c>
@@ -21537,22 +21537,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:18" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>551</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:18" ht="9.75" customHeight="1" thickBot="1"/>
@@ -21560,14 +21560,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -21820,13 +21820,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -21839,6 +21832,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -21872,11 +21872,11 @@
   <sheetData>
     <row r="1" spans="2:18" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:18" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -21895,9 +21895,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:18" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -21918,7 +21918,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -21943,7 +21943,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45998</v>
       </c>
       <c r="N4" s="99"/>
@@ -21953,12 +21953,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>475</v>
       </c>
@@ -21976,22 +21976,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:18" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>477</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:18" ht="9.75" customHeight="1" thickBot="1"/>
@@ -21999,14 +21999,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -22489,13 +22489,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -22508,6 +22501,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -22541,11 +22541,11 @@
   <sheetData>
     <row r="1" spans="2:18" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:18" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -22564,9 +22564,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:18" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -22587,7 +22587,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -22612,7 +22612,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45997</v>
       </c>
       <c r="N4" s="99"/>
@@ -22622,12 +22622,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>580</v>
       </c>
@@ -22645,22 +22645,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:18" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>581</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:18" ht="9.75" customHeight="1" thickBot="1"/>
@@ -22668,14 +22668,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -22980,6 +22980,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -22992,13 +22999,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -23032,11 +23032,11 @@
   <sheetData>
     <row r="1" spans="2:18" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:18" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -23055,9 +23055,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:18" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -23078,7 +23078,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -23103,7 +23103,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45985</v>
       </c>
       <c r="N4" s="99"/>
@@ -23113,12 +23113,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>532</v>
       </c>
@@ -23136,22 +23136,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:18" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>484</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:18" ht="9.75" customHeight="1" thickBot="1"/>
@@ -23159,14 +23159,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -23687,13 +23687,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -23706,6 +23699,13 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -23742,11 +23742,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -23765,9 +23765,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -23788,7 +23788,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -23813,7 +23813,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -23823,12 +23823,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>99</v>
       </c>
@@ -23846,22 +23846,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -23869,14 +23869,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -24273,6 +24273,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -24285,13 +24292,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -24325,11 +24325,11 @@
   <sheetData>
     <row r="1" spans="2:18" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:18" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -24348,9 +24348,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:18" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -24371,7 +24371,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:18">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -24396,7 +24396,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>46000</v>
       </c>
       <c r="N4" s="99"/>
@@ -24406,12 +24406,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:18">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>595</v>
       </c>
@@ -24429,22 +24429,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:18" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>597</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:18" ht="9.75" customHeight="1" thickBot="1"/>
@@ -24452,14 +24452,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -24760,6 +24760,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -24772,13 +24779,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -24812,11 +24812,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -24835,9 +24835,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -24858,7 +24858,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -24883,7 +24883,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -24893,12 +24893,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>85</v>
       </c>
@@ -24916,22 +24916,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -24939,14 +24939,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -25200,6 +25200,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -25212,13 +25219,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -25252,11 +25252,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -25275,9 +25275,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -25298,7 +25298,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -25323,7 +25323,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -25333,12 +25333,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>242</v>
       </c>
@@ -25356,22 +25356,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -25379,14 +25379,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -25582,6 +25582,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -25594,13 +25601,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -25634,11 +25634,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -25657,9 +25657,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -25680,7 +25680,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -25705,7 +25705,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45987</v>
       </c>
       <c r="N4" s="99"/>
@@ -25715,12 +25715,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>266</v>
       </c>
@@ -25738,22 +25738,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>233</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -25761,14 +25761,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -26138,6 +26138,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -26150,13 +26157,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -26190,11 +26190,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -26213,9 +26213,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -26236,7 +26236,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -26261,7 +26261,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -26271,12 +26271,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>269</v>
       </c>
@@ -26294,22 +26294,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>275</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -26317,14 +26317,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -26606,6 +26606,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -26618,13 +26625,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -26658,11 +26658,11 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="17" customHeight="1">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="116"/>
       <c r="E2" s="12" t="s">
         <v>24</v>
       </c>
@@ -26681,9 +26681,9 @@
       <c r="N2" s="96"/>
     </row>
     <row r="3" spans="2:14" ht="17" customHeight="1">
-      <c r="B3" s="106"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
       <c r="E3" s="4" t="s">
         <v>22</v>
       </c>
@@ -26704,7 +26704,7 @@
       <c r="N3" s="99"/>
     </row>
     <row r="4" spans="2:14">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="110" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="97"/>
@@ -26729,7 +26729,7 @@
         <v>20</v>
       </c>
       <c r="L4" s="97"/>
-      <c r="M4" s="115">
+      <c r="M4" s="111">
         <v>45972</v>
       </c>
       <c r="N4" s="99"/>
@@ -26739,12 +26739,12 @@
       <c r="N5" s="9"/>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
       <c r="F6" s="98" t="s">
         <v>282</v>
       </c>
@@ -26762,22 +26762,22 @@
       <c r="N6" s="99"/>
     </row>
     <row r="7" spans="2:14" ht="18.75" customHeight="1" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="111" t="s">
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="107" t="s">
         <v>289</v>
       </c>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
       <c r="N7" s="93"/>
     </row>
     <row r="8" spans="2:14" ht="9.75" customHeight="1" thickBot="1"/>
@@ -26785,14 +26785,14 @@
       <c r="B9" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="113"/>
-      <c r="E9" s="112" t="s">
+      <c r="D9" s="109"/>
+      <c r="E9" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="113"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -27106,6 +27106,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="F7:N7"/>
     <mergeCell ref="C9:D9"/>
@@ -27118,13 +27125,6 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:N6"/>
-    <mergeCell ref="B2:D3"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
